--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -795,6 +795,18 @@
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>이미지: images/에 같은 파일명으로 교체 → 커밋. 게임은 no로 참조하므로 코드수정 불필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>connection</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>기록관리 연결설명</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1740,6 +1752,11 @@
           <t>content</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>connection</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
@@ -1779,6 +1796,11 @@
           <t>고려 시대, 몽골이 쳐들어왔어요. 나라가 위험해지자 사람들은 부처님의 힘으로 나라를 지키고 싶었어요. 그래서 불교 경전을 나무판에 하나하나 새기기 시작했어요. 무려 16년이나 걸린 큰 프로젝트였어요.</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>나라가 위험할 때 기록을 만든다는 것은, 기록이 단순한 정보가 아니라 사람들의 소망과 의지를 담는다는 뜻이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="n">
@@ -1822,6 +1844,11 @@
           <t>나무판 81,258장에 글자를 새겼어요. 글자 수만 5,200만 자가 넘어요. 놀라운 건 틀린 글자가 거의 없다는 거예요. 나무가 썩지 않도록 특별한 처리도 했어요. 아주 꼼꼼하고 정교하게 만든 기록이에요.</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>기록을 만들 때 정확하게 만드는 것은 기록관리에서 가장 중요한 원칙이에요. 틀린 정보가 들어가면 나중에 큰 문제가 될 수 있거든요.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1865,6 +1892,11 @@
           <t>처음에는 강화도에 있다가 해인사로 옮겨졌어요. 해인사 장경판전은 바람이 잘 통하는 특별한 건물이에요. 덕분에 나무판이 770년이 넘도록 잘 보존될 수 있었어요. 한국전쟁 때 폭격 위기도 있었지만, 다행히 살아남았어요.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>기록을 오래 보관하려면 보관 장소가 아주 중요해요. 해인사 장경판전은 자연 바람으로 온도와 습도를 조절하는 아주 똑똑한 건물이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1908,6 +1940,11 @@
           <t>세계에서 가장 큰 규모의 불교 경전 목판이에요. 81,258장에 틀린 글자가 거의 없을 만큼 정교해요. 2007년에 유네스코 세계기록유산이 되었어요.</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>기록이 세계기록유산이 되려면 '이 기록이 왜 중요한지'를 설명할 수 있어야 해요. 기록의 가치를 판단하는 것도 기록 전문가의 중요한 일이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2068,6 +2105,11 @@
           <t>금속으로 글자 하나하나를 만들어서 판에 끼우고 인쇄했어요. 이것을 '금속활자 인쇄'라고 해요. 독일 구텐베르크가 금속활자로 성경을 찍은 것보다 78년이나 앞선 기술이에요!</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>기록을 만드는 기술은 시대마다 달라요. 금속활자는 같은 내용을 여러 번 찍을 수 있어서, 기록을 널리 퍼뜨리는 데 아주 중요한 발명이었어요.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2306,6 +2348,11 @@
           <t>사관이라는 기록 전문가가 왕 옆에서 모든 것을 적었어요. 왕이 뭐라고 말했는지, 누구를 만났는지 다 기록했어요. 놀라운 점은 왕도 이 기록을 볼 수 없었다는 거예요! 기록이 바뀌지 않도록 지킨 거예요.</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>기록을 만드는 사람이 누구의 눈치도 보지 않는 것은 오늘날에도 아주 중요한 원칙이에요. 기록 전문가는 누구의 압력에도 기록을 바꾸면 안 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2349,6 +2396,11 @@
           <t>임진왜란이 일어나자 4곳에 있던 실록 중 3곳이 불에 탔어요. 전주에 있던 1부만 살아남았어요. 마을 사람들이 산속에 숨겨서 지켰거든요. 전쟁이 끝나고 나라에서 다시 5부를 만들어 5곳에 나누어 보관했어요.</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>중요한 기록은 한 곳에만 두면 위험해요. 여러 곳에 나누어 보관하는 것을 '분산 보존'이라고 해요. 지금도 기록 전문가들이 꼭 지키는 원칙이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2392,6 +2444,11 @@
           <t>472년 동안 한 나라의 역사를 빠짐없이 기록한 건 세계에서 조선왕조실록이 유일해요. 1997년에 유네스코 세계기록유산이 되었어요.</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>이 기록이 특별한 이유는 '빠짐없이' 기록했다는 거예요. 기록에 빈 구멍이 없다는 것은 그 기록의 가치를 아주 높여줘요.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2474,6 +2531,11 @@
           <t>조선왕조실록 홈페이지(sillok.history.go.kr)에서 누구나 무료로 읽을 수 있어요. 한글 번역도 되어 있어서 어린이도 찾아볼 수 있어요.</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>원본은 보호하면서 내용은 누구나 볼 수 있게 하는 것, 이것이 기록 서비스의 가장 좋은 모습이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2595,6 +2657,11 @@
           <t>일제강점기와 한국전쟁이라는 큰 위기를 겪었어요. 소장자가 목숨을 걸고 지켜냈어요. 1940년에 경북 안동에서 다시 발견되었어요. 전 세계에 딱 1권만 남아 있는 아주 귀한 책이에요.</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>딱 1권만 남은 기록은 잃어버리면 영원히 사라져요. 그래서 기록 전문가들은 중요한 기록은 꼭 복사본을 만들어 여러 곳에 보관해요.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2638,6 +2705,11 @@
           <t>글자를 만든 원리를 설명한 책이 남아 있는 건 세계에서 훈민정음이 유일해요. 1997년에 유네스코 세계기록유산이 되었어요.</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>세상에 하나밖에 없는 기록은 그 자체로 엄청난 가치가 있어요. 기록의 가치를 판단하는 것도 기록 전문가의 중요한 일이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2915,6 +2987,11 @@
           <t>아산 현충사 유물관에 국보 제76호로 보존되어 있어요. 온도와 습도를 맞춘 특별한 시설에서 관리하고 있어요.</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>오래된 종이 기록을 지키려면 온도와 습도를 잘 맞춰야 해요. 너무 덥거나 습하면 종이가 상하거든요. 이것을 관리하는 게 기록 전문가의 중요한 일이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -3036,6 +3113,11 @@
           <t>허준이 혼자서 썼지만, 왕실의 도움을 받았어요. 총 25권으로, 몸의 안과 밖, 여러 가지 병, 약, 침과 뜸까지 다 정리했어요. 한글로 약 이름을 적어서 일반 사람도 알 수 있게 했어요.</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>기록을 만들 때 누구나 이해할 수 있게 쓰는 것은 아주 중요해요. 허준은 한자만 쓰지 않고 한글도 함께 써서 더 많은 사람이 읽을 수 있게 했어요.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3196,6 +3278,11 @@
           <t>인터넷 한국고전종합DB에서 원문과 번역을 읽을 수 있어요. 서울 강서구에 있는 허준박물관에 가면 관련 전시를 볼 수 있어요.</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>기록을 인터넷에 올려서 누구나 볼 수 있게 하는 것을 '디지털 서비스'라고 해요. 기록 전문가의 중요한 일 중 하나예요.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3278,6 +3365,11 @@
           <t>돈을 모은 사람들의 명단, 영수증, 신문 기사, 단체들의 편지 등 다양한 기록이 만들어졌어요. 당시 신문들이 이 운동을 적극적으로 알려서 기록이 많이 남았어요.</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>하나의 사건에 대해 여러 종류의 기록이 있으면 더 정확하게 알 수 있어요. 명단, 영수증, 신문 기사가 서로를 확인해 주거든요.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -3321,6 +3413,11 @@
           <t>일제가 이 운동을 막으려 했지만, 신문 기사와 개인이 보관한 문서 덕분에 기록이 살아남았어요. 광복 후에 학자들이 흩어진 기록을 다시 모았어요.</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>누군가가 기록을 없애려 해도, 여러 곳에 흩어져 있으면 완전히 없앨 수 없어요. 이것이 기록을 여러 곳에 보관하는 이유예요.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -3364,6 +3461,11 @@
           <t>국민이 스스로 나서서 나라를 지키려 한 운동의 기록이에요. 2017년에 유네스코 세계기록유산이 되었어요.</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>보통 사람들이 만든 기록도 아주 중요해요. 정부가 만든 기록만으로는 알 수 없는 이야기가 담겨 있거든요.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -3524,6 +3626,11 @@
           <t>군대와 경찰이 쓴 문서, 재판 기록, 피해를 입은 사람들의 이야기, 현장 사진 등이 있어요. 피해를 준 쪽과 피해를 입은 쪽, 양쪽의 기록이 모두 남아 있어요.</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>한쪽의 기록만 있으면 진실을 알기 어려워요. 여러 쪽의 기록이 모두 있어야 무슨 일이 있었는지 제대로 알 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -3567,6 +3674,11 @@
           <t>오랫동안 이 일에 대해 말하는 것이 금지되었어요. 피해자들도 이야기하기를 두려워했어요. 2000년에 특별법이 만들어진 후에야 기록을 모으고 진실을 밝히기 시작했어요.</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>기록이 숨겨지면 진실도 숨겨져요. 기록을 지키고 공개하는 것은 진실을 밝히는 가장 중요한 방법이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -3610,6 +3722,11 @@
           <t>숨겨졌던 진실을 밝히는 데 기록이 얼마나 중요한지 보여줘요. 2025년에 유네스코 세계기록유산이 되었어요.</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>아픈 역사의 기록도 소중하게 보관해야 해요. 같은 슬픔이 반복되지 않도록 하는 것이 기록의 힘이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -3653,6 +3770,11 @@
           <t>제주4·3평화재단, 국가기록원 등에 보관되어 있어요. 제주4·3평화기념관에서 기록물을 보존하고 전시하고 있어요. 사람들의 이야기를 녹음해서 모으는 작업도 하고 있어요.</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>사람들의 이야기를 녹음해서 기록으로 남기는 것을 '구술 기록'이라고 해요. 문서에 없는 생생한 이야기를 보존하는 중요한 방법이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -3774,6 +3896,11 @@
           <t>학생들이 쓴 선언문, 시위 현장 사진과 영상, 정부 문서, 신문 기사 등이 있어요. 시민들과 기자들이 현장에서 직접 찍은 사진이 많아요.</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>사건이 일어나는 바로 그 순간에 만들어진 기록은 아주 귀해요. 나중에 기억으로 쓴 것보다 훨씬 정확하거든요.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -3856,6 +3983,11 @@
           <t>아시아에서 처음으로 학생과 시민이 힘을 모아 이룬 민주혁명의 기록이에요. 2023년에 유네스코 세계기록유산이 되었어요.</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>학생들과 시민들이 직접 만든 기록은 그 시대를 가장 생생하게 보여줘요. 기록은 그 시대를 살았던 사람들의 목소리예요.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -3899,6 +4031,11 @@
           <t>국가기록원, 4·19혁명기념도서관 등에 보관되어 있어요. 디지털로 만드는 작업이 진행 중이에요.</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>오래된 기록을 디지털로 바꾸면 더 안전하게 보관할 수 있고, 더 많은 사람이 볼 수 있어요.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -4098,6 +4235,11 @@
           <t>전쟁으로 망가진 산을 되살린 건 세계에서 우리나라가 거의 유일해요. 다른 나라들의 본보기가 되는 기록이에요. 2025년에 유네스코 세계기록유산이 되었어요.</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>성공한 경험을 기록으로 남기면 다른 사람들도 배울 수 있어요. 기록은 미래를 위한 선물이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -4258,6 +4400,11 @@
           <t>시민들이 쓴 글, 현장 사진과 영상, 군대 문서, 외국 뉴스 보도, 피해자들의 이야기 등 다양한 형태의 기록이 만들어졌어요. 여러 사람이 여러 방법으로 남긴 기록이에요.</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>한 사건에 대해 여러 사람이 여러 방법으로 기록하면, 더 완전한 이야기를 알 수 있어요. 이것을 '다원적 기록'이라고 해요.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -4301,6 +4448,11 @@
           <t>군사 정권은 진실을 숨기려 했어요. 하지만 시민들이 사진과 영상을 몰래 보관했어요. 민주화가 된 후에 숨겨졌던 군대 문서도 공개되었고, 기록이 체계적으로 모아졌어요.</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>기록을 숨기려는 힘과 기록을 지키려는 힘이 싸울 때, 결국 기록을 지키는 쪽이 이겨요. 기록은 진실의 편이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -4344,6 +4496,11 @@
           <t>시민들이 민주주의를 지키기 위해 싸운 기록이에요. 전 세계 민주화운동의 본보기로 평가받아요. 2011년에 유네스코 세계기록유산이 되었어요.</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>이 기록이 세계기록유산이 된 건, 한 나라의 이야기가 아니라 전 세계 사람들에게 중요한 교훈이기 때문이에요.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -4387,6 +4544,11 @@
           <t>광주 5·18민주화운동기록관에 주요 기록이 보관되어 있어요. 국가기록원에도 관련 기록이 있어요. 사람들의 이야기를 녹음해서 모으는 작업도 계속하고 있어요.</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>살아 있는 사람들의 이야기를 지금 기록하지 않으면, 시간이 지나면 영원히 사라져요. 그래서 '구술 기록'은 서두를수록 좋아요.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -4508,6 +4670,11 @@
           <t>생방송 녹화 테이프 463개, 가족을 찾는 신청서 2만 건 이상, 프로듀서의 업무 수첩 등이 있어요. TV 방송으로 만들어진 기록이라는 점이 특별해요.</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>기록은 종이에만 있는 게 아니에요. 비디오테이프, 사진, 음성 파일도 모두 소중한 기록이에요. 기록의 형태는 시대에 따라 달라져요.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -4588,6 +4755,11 @@
       <c r="I71" s="7" t="inlineStr">
         <is>
           <t>TV 방송으로 헤어진 가족을 찾아준 기록이에요. 전쟁의 슬픔을 보여주는 소중한 기록이에요. 2015년에 유네스코 세계기록유산이 되었어요.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>기록은 사람들의 아픔과 기쁨을 담아요. 이산가족이 다시 만나는 장면은 기록이 가진 감동의 힘을 보여줘요.</t>
         </is>
       </c>
     </row>

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -10,6 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="content" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="levels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="badges" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4844,4 +4847,418 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>기록 루키</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>level1.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>기록 헌터</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>level2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>기록 레인저</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>level3.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>기록 가디언</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>level4.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>기록 마스터</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>level5.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>기록 레전드</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>level6.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>emoji</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>고려</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🏛️</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>고려 기록 전문가</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>고려 시대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>📜</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>조선 기록 전문가</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>조선 시대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>근현대</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>📷</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>근현대 기록 전문가</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>근현대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🏆</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>한국 기록 수호자</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>모든 시대의 기록 유산을 완료했습니다! 당신은 진정한 기록 수호자입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>생산 배경</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>이 기록은 왜 만들어졌는가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>생산 방법</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>누가, 어떻게 만들었는가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>생존 이야기</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>어떻게 현재까지 남게 되었는가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기록문화적 가치</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>왜 이 기록이 중요한가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>현재 보존 방법</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>지금은 어떻게 보존되고 있는가?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>접근·열람 방법</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>일반인이 이 기록을 보려면?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -4999,7 +4999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5028,6 +5028,11 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5047,12 +5052,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>고려 기록 전문가</t>
+          <t>고려 컬렉터</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>고려 시대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>badge_goryeo.png</t>
         </is>
       </c>
     </row>
@@ -5074,12 +5084,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>조선 기록 전문가</t>
+          <t>조선 컬렉터</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>조선 시대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>badge_joseon.png</t>
         </is>
       </c>
     </row>
@@ -5101,12 +5116,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>근현대 기록 전문가</t>
+          <t>근현대 컬렉터</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>근현대의 모든 기록 유산을 완료했습니다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>badge_modern.png</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5148,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>한국 기록 수호자</t>
+          <t>올 컴플리트</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>모든 시대의 기록 유산을 완료했습니다! 당신은 진정한 기록 수호자입니다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>badge_allcomplete.png</t>
         </is>
       </c>
     </row>

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>고려 시대의 모든 기록 유산을 완료했습니다.</t>
+          <t>고려 시대의 기록 유산을 모두 수집했습니다! 고려의 기록을 끝까지 지켜낸 컬렉터예요.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조선 시대의 모든 기록 유산을 완료했습니다.</t>
+          <t>조선 시대의 기록 유산을 모두 수집했습니다! 조선 왕조의 기록을 빠짐없이 모았어요.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>근현대의 모든 기록 유산을 완료했습니다.</t>
+          <t>근현대의 기록 유산을 모두 수집했습니다! 격동의 시대를 담은 기록을 지켜냈어요.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>모든 시대의 기록 유산을 완료했습니다! 당신은 진정한 기록 수호자입니다.</t>
+          <t>고려·조선·근현대, 모든 시대의 기록을 완성했습니다! 흩어진 기록을 전부 구해낸 최고의 기록 수호자예요.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -4855,7 +4855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4879,6 +4879,11 @@
           <t>icon</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>icon_b</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -4897,6 +4902,11 @@
           <t>level1.png</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>level1b.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -4915,6 +4925,11 @@
           <t>level2.png</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>level2b.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4933,6 +4948,11 @@
           <t>level3.png</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>level3b.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -4951,6 +4971,11 @@
           <t>level4.png</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>level4b.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4969,6 +4994,11 @@
           <t>level5.png</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>level5b.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4985,6 +5015,11 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>level6.png</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>level6b.png</t>
         </is>
       </c>
     </row>

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -914,6 +914,11 @@
           <t>image_note</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
@@ -978,6 +983,11 @@
           <t>해인사 대장경판(목판)</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>사진: 해인사 대장경판 ⓒSteve46814, CC BY-SA 3.0 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -1042,6 +1052,11 @@
           <t>원본 소장 프랑스국립도서관(BnF)</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>사진: 직지심체요절, 퍼블릭도메인/CC0 (Wikimedia Commons) · 원본 소장 프랑스국립도서관(BnF)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -1106,6 +1121,11 @@
           <t>태백산사고본</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>사진: 조선왕조실록(태백산사고본), 국가유산청 · 공공누리 제1유형</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -1170,6 +1190,11 @@
           <t>국보 / 원본 소장 간송미술문화재단</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>사진: 훈민정음 해례본, 퍼블릭도메인 (Wikimedia Commons) · 원본 소장 간송미술문화재단</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
@@ -1234,6 +1259,11 @@
           <t>임진장초</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>사진: 난중일기, 국가유산청 · 퍼블릭도메인 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -1298,6 +1328,11 @@
           <t>동의보감 본문(신형장부도)</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>사진: 동의보감 ⓒUlrich Lange, CC BY 4.0 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -1362,6 +1397,11 @@
           <t>국채보상운동 기록물 전시</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>사진: 국채보상운동 기록물, CC BY 4.0 (Wikimedia Commons)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -1426,6 +1466,11 @@
           <t>형무소에서 보내 온 엽서</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>사진: 제주4·3 기록물(형무소에서 보내 온 엽서), 국가유산청 유네스코 세계기록유산</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -1490,6 +1535,11 @@
           <t>1960 가두시위 / 원소장처·이용허락 확인 필요</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>사진: 4·19혁명 기록물, 출처: 유네스코한국위원회(UNESCO 세계기록유산 소개)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -1554,6 +1604,11 @@
           <t>영일지구 사방사업 전후 / 이용허락 확인 권장</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>사진: 산림녹화 기록물 — 영일지구 사방사업, ⓒKorea Society of Forest Policy · UNESCO 세계기록유산</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -1618,6 +1673,11 @@
           <t>시민 기록 문서 / 이용허락 확인 필요</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>사진: 5·18 민주화운동 기록물, 출처: UNESCO 국제기록유산센터 · ⓒ국가기록원·광주광역시·5·18기념재단</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1680,6 +1740,11 @@
       <c r="N13" s="8" t="inlineStr">
         <is>
           <t>이산가족 기록물 모음 / 이용범위 확인 필요</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>사진: KBS 특별생방송 '이산가족을 찾습니다' 기록물 ⓒ한국방송공사(KBS) · KBS 아카이브</t>
         </is>
       </c>
     </row>

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="levels" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="badges" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labels" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5386,4 +5387,66 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>connectionTitle</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>추가 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>codePrompt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>코드를 입력하세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>codeSubmit</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -5395,7 +5395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5446,6 +5446,114 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>toastSave</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기록 저장 성공!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>completeTitle</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>기록 완성!</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>completeMeta</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{country} · UNESCO {year}년 등재</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>completeSourceFallback</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>사진 출처 확인 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>levelUpNext</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>축하합니다! 다음은 '{next}'에 도전하세요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>levelUpMax</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>축하합니다! 최고 등급에 도달했어요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>badgeLocked</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>아직 획득하지 못한 배지예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>codeWrong</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>코드가 틀렸습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>codeIncomplete</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3자리를 모두 입력하세요.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="badges" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quizzes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5395,7 +5396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5554,6 +5555,498 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quizTitle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>배지 획득 퀴즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quizGuide</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>타임라인에서 해당 기록유산을 다시 확인한 뒤 도전하세요!</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>era</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>opt1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>opt2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>opt3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>opt4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>고려</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>사진을 보고 이 기록유산의 이름을 맞혀보세요.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>해인사 대장경판</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>직지심체요절</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>훈민정음 해례본</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>고려</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>직지심체요절이 세계적으로 중요한 이유는?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>세계에서 가장 두꺼운 책이라서</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>세계에서 가장 오래된 금속활자 인쇄물이라서</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>세계 최초의 한글 책이라서</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>그림이 가장 많은 책이라서</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>고려</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>해인사 대장경판이 770년 넘게 잘 보존된 비결은?</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>깊은 땅속 금고에 넣어두어서</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>물에 담가 보관해서</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>바람이 잘 통해 온·습도가 조절되는 장경판전에 보관해서</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>해마다 새 나무판으로 바꿔서</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>사진을 보고 이 기록유산의 이름을 맞혀보세요.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>훈민정음 해례본</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>난중일기</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>동의보감</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>조선왕조실록의 특별한 점으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>왕도 함부로 볼 수 없게 하여 기록을 그대로 지켰다</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>왕이 매일 직접 썼다</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>외국 사람이 대신 써 주었다</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100년 동안만 기록했다</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>조선</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>난중일기는 어떤 기록인가요?</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>이순신 장군이 임진왜란 동안 전쟁터에서 직접 쓴 일기</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>세종대왕이 쓴 일기</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>허준이 쓴 의학책</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>왕의 비서가 쓴 회의록</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>근현대</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>사진을 보고 이 기록유산의 이름을 맞혀보세요.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KBS 이산가족을 찾습니다</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4·19혁명 기록물</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5·18 민주화운동 기록물</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>국채보상운동 기록물</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>근현대</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>국채보상운동은 어떤 운동이었나요?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>일본에 진 나라의 빚을 국민이 힘을 모아 갚으려 한 운동</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>일본과 무역을 늘리자는 운동</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>새로운 화폐를 만들자는 운동</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>외국에 돈을 빌려주자는 운동</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>근현대</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4·19혁명이 일어난 까닭으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>부정선거에 맞서 공정한 선거를 요구하며 학생과 시민이 일어나서</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>외국의 침입을 막기 위해</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>새로운 왕을 세우기 위해</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>세금을 낮춰 달라고 해서</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -5590,7 +5590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,26 +5671,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>훈민정음 해례본</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>해인사 대장경판</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>직지심체요절</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>훈민정음 해례본</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>조선왕조실록</t>
-        </is>
-      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5714,26 +5714,26 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>세계 최초의 한글 책이라서</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>그림이 가장 많은 책이라서</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>세계에서 가장 두꺼운 책이라서</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>세계에서 가장 오래된 금속활자 인쇄물이라서</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>세계 최초의 한글 책이라서</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>그림이 가장 많은 책이라서</t>
-        </is>
-      </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -5757,26 +5757,26 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>바람이 잘 통해 온·습도가 조절되는 장경판전에 보관해서</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>해마다 새 나무판으로 바꿔서</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>깊은 땅속 금고에 넣어두어서</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>물에 담가 보관해서</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>바람이 잘 통해 온·습도가 조절되는 장경판전에 보관해서</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>해마다 새 나무판으로 바꿔서</t>
-        </is>
-      </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -5805,26 +5805,26 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>동의보감</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>훈민정음 해례본</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>조선왕조실록</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>난중일기</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>동의보감</t>
-        </is>
-      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5848,26 +5848,26 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>왕이 매일 직접 썼다</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>외국 사람이 대신 써 주었다</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>100년 동안만 기록했다</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>왕도 함부로 볼 수 없게 하여 기록을 그대로 지켰다</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>왕이 매일 직접 썼다</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>외국 사람이 대신 써 주었다</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100년 동안만 기록했다</t>
-        </is>
-      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -5891,26 +5891,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>허준이 쓴 의학책</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>왕의 비서가 쓴 회의록</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>이순신 장군이 임진왜란 동안 전쟁터에서 직접 쓴 일기</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>세종대왕이 쓴 일기</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>허준이 쓴 의학책</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>왕의 비서가 쓴 회의록</t>
-        </is>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -5939,26 +5939,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>국채보상운동 기록물</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>KBS 이산가족을 찾습니다</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4·19혁명 기록물</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>5·18 민주화운동 기록물</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>국채보상운동 기록물</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6025,26 +6025,162 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>외국의 침입을 막기 위해</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>새로운 왕을 세우기 위해</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>세금을 낮춰 달라고 해서</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>부정선거에 맞서 공정한 선거를 요구하며 학생과 시민이 일어나서</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>외국의 침입을 막기 위해</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>새로운 왕을 세우기 위해</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>세금을 낮춰 달라고 해서</t>
-        </is>
-      </c>
       <c r="J10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>올컴플리트</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>photo</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>사진을 보고 이 기록유산의 이름을 맞혀보세요.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>동의보감</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>직지심체요절</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>난중일기</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>올컴플리트</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>전쟁이 끝난 뒤 민둥산을 푸른 숲으로 되살린, 세계에서 거의 유일한 성공 사례로 꼽히는 기록유산은?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>국채보상운동 기록물</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KBS 이산가족을 찾습니다</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>산림녹화 기록물</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>제주4·3 기록물</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>올컴플리트</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>다음 중 가장 먼저(오래전에) 만들어진 기록유산은?</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>직지심체요절</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>조선왕조실록</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>동의보감</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>해인사 대장경판</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -5396,7 +5396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5576,6 +5576,102 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>타임라인에서 해당 기록유산을 다시 확인한 뒤 도전하세요!</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>endConfirmTitle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>결과를 확인하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>endConfirmMsg</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>플레이 기록이 사라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>endConfirmYes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>네</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>endConfirmNo</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>아니오</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>resultSecLevel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>최종 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>resultSecBadges</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>최종 획득 배지</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>resultSecRecord</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>수집 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>resultSave</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>저장</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6205,6 @@
           <t>text</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>전쟁이 끝난 뒤 민둥산을 푸른 숲으로 되살린, 세계에서 거의 유일한 성공 사례로 꼽히는 기록유산은?</t>
@@ -6153,7 +6248,6 @@
           <t>text</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>다음 중 가장 먼저(오래전에) 만들어진 기록유산은?</t>

--- a/content/기록문화_초등_콘텐츠.xlsx
+++ b/content/기록문화_초등_콘텐츠.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sections" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labels" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quizzes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tutorial" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5396,7 +5397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5672,6 +5673,30 @@
       <c r="B23" t="inlineStr">
         <is>
           <t>저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>resultEmptyBadges</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>아직 획득한 배지가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>resultEmptyRecords</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>아직 완성한 기록유산이 없어요.</t>
         </is>
       </c>
     </row>
@@ -6280,4 +6305,95 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>body</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>우리는 기록 수호대!</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>{name} {level} 환영합니다. 지금부터 우리는 여러 시대의 기록을 구하는 임무를 수행합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>흩어진 기록을 구하라!</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>우리의 소중한 기록 유산이 일부가 사라졌습니다. 사라진 기록을 찾아 숫자 코드를 입력하면 기록이 복원됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>시대의 배지를 모아라!</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>한 시대의 기록을 모두 복원하면 배지 퀴즈가 열립니다. 퀴즈를 통과해 시대 배지를 획득하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>우리가 기록을 구한다!</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{name} {level} 모든 준비가 끝났습니다. 지금 바로 기록을 구하러 출발하세요!</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>